--- a/pseudodata/1121.xlsx
+++ b/pseudodata/1121.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,24 +536,24 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0003814970779678819</v>
+        <v>0.0001802486539502805</v>
       </c>
       <c r="M2" t="n">
-        <v>5.674943025261526e-05</v>
+        <v>0.001022932081695123</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.90748538983941e-05</v>
+        <v>9.012432697514023e-06</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -590,24 +590,24 @@
         <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0008113212640843247</v>
+        <v>-2.104595530933435e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>7.256332256218779e-05</v>
+        <v>0.001041781600269328</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.056606320421624e-05</v>
+        <v>-1.052297765466718e-06</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -644,24 +644,24 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00149741110476104</v>
+        <v>-0.0002476343798990645</v>
       </c>
       <c r="M4" t="n">
-        <v>9.87979418305292e-05</v>
+        <v>0.001139650159357878</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.487055523805199e-05</v>
+        <v>-1.238171899495322e-05</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -698,24 +698,24 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.002475430329128391</v>
+        <v>-0.0004783681595870716</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001385179140788122</v>
+        <v>0.00132618219133069</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0001237715164564195</v>
+        <v>-2.391840797935358e-05</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -752,24 +752,24 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.003771134308714094</v>
+        <v>-0.0007023291922937522</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001950827826417789</v>
+        <v>0.001623456616056035</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0001885567154357047</v>
+        <v>-3.511645961468761e-05</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -806,24 +806,24 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00539378525387212</v>
+        <v>-0.0009151818471197386</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002699936407691933</v>
+        <v>0.002064650861855071</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.000269689262693606</v>
+        <v>-4.575909235598693e-05</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -860,24 +860,24 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.007262191128479314</v>
+        <v>-0.001117104927919099</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0003619533027887063</v>
+        <v>0.002693270760596351</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0003631095564239657</v>
+        <v>-5.585524639595496e-05</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -908,13 +908,13 @@
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -922,16 +922,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.799804105675328e-05</v>
+        <v>-0.001311381502804765</v>
       </c>
       <c r="M9" t="n">
-        <v>8.025581392019452e-05</v>
+        <v>0.00356363761472211</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.999020528376642e-07</v>
+        <v>-6.556907514023822e-05</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -962,13 +962,13 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0001503730594287792</v>
+        <v>-0.001502399985171341</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0001026200348982996</v>
+        <v>0.004742488548542998</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.518652971438962e-06</v>
+        <v>-7.511999925856703e-05</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1016,13 +1016,13 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.000276680306990895</v>
+        <v>-0.00169271275757035</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0001397213892712825</v>
+        <v>0.006303187854451726</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.383401534954475e-05</v>
+        <v>-8.463563787851754e-05</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0003969313256235557</v>
+        <v>-0.001881164054567974</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0001958939127218873</v>
+        <v>0.008294552812714786</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.984656628117779e-05</v>
+        <v>-9.405820272839868e-05</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.000513532491621951</v>
+        <v>-0.002065766332522001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0002758887169974864</v>
+        <v>0.010686681428485</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.567662458109755e-05</v>
+        <v>-0.0001032883166261001</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1178,13 +1178,13 @@
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0006269446775045515</v>
+        <v>-0.002251557952902621</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0003818286685302826</v>
+        <v>0.01337363739534133</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.134723387522758e-05</v>
+        <v>-0.0001125778976451311</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1232,13 +1232,13 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0007416521209771273</v>
+        <v>-0.002451990466522035</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000511879269749524</v>
+        <v>0.01632171425154224</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.708260604885637e-05</v>
+        <v>-0.0001225995233261018</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1286,30 +1286,30 @@
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0002000167094429866</v>
+        <v>-0.002674887968998579</v>
       </c>
       <c r="M16" t="n">
-        <v>8.025581392019452e-05</v>
+        <v>0.01971482798240609</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000083547214933e-05</v>
+        <v>-0.000133744398449929</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1340,30 +1340,30 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0001822469860228251</v>
+        <v>-0.0029107652281373</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001026200348982996</v>
+        <v>0.02385105939384964</v>
       </c>
       <c r="N17" t="n">
-        <v>9.112349301141253e-06</v>
+        <v>-0.000145538261406865</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1394,30 +1394,30 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0001235661798399115</v>
+        <v>-0.003138120433778448</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0001397213892712825</v>
+        <v>0.02881061135062982</v>
       </c>
       <c r="N18" t="n">
-        <v>6.178308991995578e-06</v>
+        <v>-0.0001569060216889224</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1425,600 +1425,6 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>100</v>
-      </c>
-      <c r="L19" t="n">
-        <v>4.916648823831516e-05</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0001958939127218873</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.458324411915758e-06</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-2.488183590711675e-05</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.0002758887169974864</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-1.244091795355838e-06</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>100</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-8.780606932733779e-05</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0003818286685302826</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-4.39030346636689e-06</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.0001399486263378529</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.000511879269749524</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-6.997431316892645e-06</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>100</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>50</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-3.595225925630234e-05</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8.025581392019452e-05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-1.797612962815117e-06</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>100</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>50</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>100</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2.740682231001193e-07</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.0001026200348982996</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.370341115500597e-08</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>100</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>50</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>100</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2.996032434466753e-05</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.0001397213892712825</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.498016217233377e-06</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>100</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>50</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>100</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5.474113329847009e-05</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.0001958939127218873</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.737056664923505e-06</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>100</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>50</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>100</v>
-      </c>
-      <c r="L27" t="n">
-        <v>7.564281717512288e-05</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.0002758887169974864</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.782140858756144e-06</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>100</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>50</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>100</v>
-      </c>
-      <c r="L28" t="n">
-        <v>9.255890471293585e-05</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.0003818286685302826</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.627945235646793e-06</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>100</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>50</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>100</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.0001064806099699354</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.000511879269749524</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5.324030498496773e-06</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
         <v>1</v>
       </c>
     </row>
